--- a/data/trans_dic/P1423-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P1423-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con enfermedades crónicas de salud mental (trastornos depresivos o ansiedad)</t>
+          <t>Población con enfermedades crónicas de salud mental (trastornos depresivos o ansiedad) (tasa de respuesta: 99,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,32; 5,06</t>
+          <t>1,06; 4,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,89; 8,05</t>
+          <t>2,88; 7,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,74; 8,4</t>
+          <t>2,75; 8,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,92</t>
+          <t>0,59; 3,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,96; 14,64</t>
+          <t>6,51; 14,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,84; 17,05</t>
+          <t>8,74; 16,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,67; 19,14</t>
+          <t>10,59; 19,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,42; 7,01</t>
+          <t>3,52; 7,04</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,34; 8,75</t>
+          <t>4,6; 8,85</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,63; 11,26</t>
+          <t>6,51; 11,23</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,27; 12,48</t>
+          <t>7,28; 12,52</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,35; 4,68</t>
+          <t>2,42; 4,62</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,39; 4,13</t>
+          <t>1,23; 4,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,09; 6,26</t>
+          <t>2,15; 6,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,75; 4,98</t>
+          <t>1,69; 4,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,63; 7,89</t>
+          <t>3,63; 8,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,78; 11,86</t>
+          <t>6,55; 11,82</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,6; 15,61</t>
+          <t>9,55; 15,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,19; 12,59</t>
+          <t>7,12; 12,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,11; 16,12</t>
+          <t>11,29; 16,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,46; 7,4</t>
+          <t>4,57; 7,43</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,48; 10,07</t>
+          <t>6,46; 10,18</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,1; 8,36</t>
+          <t>5,07; 8,15</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,86; 11,49</t>
+          <t>7,88; 11,39</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,28</t>
+          <t>0,3; 3,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,99; 8,39</t>
+          <t>3,1; 8,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,06</t>
+          <t>0,31; 3,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,98; 12,2</t>
+          <t>6,15; 12,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,29; 9,97</t>
+          <t>4,27; 9,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,2; 15,03</t>
+          <t>8,09; 15,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,57; 11,62</t>
+          <t>5,38; 11,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,19; 18,4</t>
+          <t>12,43; 18,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,6; 5,78</t>
+          <t>2,63; 5,8</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,33; 10,72</t>
+          <t>6,26; 10,49</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,21; 6,66</t>
+          <t>3,32; 6,57</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,18; 14,56</t>
+          <t>10,04; 14,35</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 4,2</t>
+          <t>0,93; 4,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,13; 5,43</t>
+          <t>1,11; 4,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,34; 5,01</t>
+          <t>1,4; 5,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,11; 12,22</t>
+          <t>5,1; 11,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,7; 7,13</t>
+          <t>2,77; 7,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,45; 17,12</t>
+          <t>10,69; 17,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,62; 10,02</t>
+          <t>4,37; 9,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,68; 11,04</t>
+          <t>4,66; 11,04</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,2; 4,94</t>
+          <t>2,15; 4,82</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,42; 10,38</t>
+          <t>6,15; 10,38</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,42; 6,72</t>
+          <t>3,59; 6,63</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,6; 10,36</t>
+          <t>5,74; 10,22</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,66; 6,95</t>
+          <t>1,68; 6,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,44; 8,64</t>
+          <t>2,41; 8,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,81; 9,54</t>
+          <t>3,0; 9,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,67; 4,1</t>
+          <t>0,66; 4,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,38; 15,15</t>
+          <t>6,94; 15,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,73; 26,86</t>
+          <t>15,27; 26,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,63; 17,66</t>
+          <t>8,53; 17,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,32; 9,16</t>
+          <t>2,98; 8,99</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,52; 9,51</t>
+          <t>4,66; 9,8</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,7; 16,21</t>
+          <t>9,55; 16,25</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,91; 12,2</t>
+          <t>6,7; 12,02</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,72; 6,16</t>
+          <t>2,9; 6,08</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,41</t>
+          <t>0,0; 2,3</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,94; 9,12</t>
+          <t>2,91; 8,8</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,1; 5,23</t>
+          <t>1,07; 4,91</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,31; 13,73</t>
+          <t>7,4; 13,46</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,04; 9,01</t>
+          <t>3,28; 8,55</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,54; 17,74</t>
+          <t>9,85; 17,87</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,01; 17,04</t>
+          <t>9,21; 17,11</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,16; 18,98</t>
+          <t>11,9; 18,39</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,87; 5,03</t>
+          <t>1,89; 4,99</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6,94; 12,25</t>
+          <t>6,81; 11,98</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5,69; 10,01</t>
+          <t>5,7; 10,4</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,48; 15,26</t>
+          <t>10,43; 15,05</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,49</t>
+          <t>1,86; 4,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,61; 7,19</t>
+          <t>3,56; 7,5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,99</t>
+          <t>1,27; 3,81</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,3; 9,85</t>
+          <t>5,26; 9,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,22; 10,75</t>
+          <t>6,01; 10,35</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,01; 11,36</t>
+          <t>7,03; 11,25</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,44; 10,8</t>
+          <t>6,68; 11,14</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,8; 16,01</t>
+          <t>5,69; 16,18</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,37; 6,98</t>
+          <t>4,35; 6,88</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5,93; 8,69</t>
+          <t>5,82; 8,88</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4,22; 6,78</t>
+          <t>4,3; 6,95</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,13; 12,01</t>
+          <t>6,27; 12,06</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,27; 7,58</t>
+          <t>4,31; 7,94</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,59</t>
+          <t>1,81; 4,43</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,03; 5,99</t>
+          <t>2,95; 5,78</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,49; 5,55</t>
+          <t>1,6; 5,91</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,66; 9,62</t>
+          <t>5,68; 9,41</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,8; 10,61</t>
+          <t>6,51; 10,62</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,29; 13,89</t>
+          <t>9,24; 13,97</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>9,75; 13,61</t>
+          <t>9,8; 13,66</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5,38; 7,96</t>
+          <t>5,4; 8,16</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4,67; 7,12</t>
+          <t>4,75; 7,28</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6,62; 9,44</t>
+          <t>6,64; 9,6</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,63; 8,96</t>
+          <t>4,42; 9,0</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,52; 3,7</t>
+          <t>2,52; 3,74</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,48; 4,95</t>
+          <t>3,47; 4,93</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,71; 3,93</t>
+          <t>2,69; 3,91</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,52; 6,7</t>
+          <t>4,5; 6,62</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,71; 8,54</t>
+          <t>6,72; 8,53</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,24; 12,41</t>
+          <t>10,32; 12,51</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,24; 11,27</t>
+          <t>9,13; 11,25</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8,97; 12,34</t>
+          <t>9,01; 12,27</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,88; 5,99</t>
+          <t>4,91; 5,96</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7,23; 8,59</t>
+          <t>7,26; 8,56</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6,14; 7,43</t>
+          <t>6,26; 7,49</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>7,44; 9,39</t>
+          <t>7,33; 9,33</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con enfermedades crónicas de salud mental (trastornos depresivos o ansiedad)</t>
+          <t>Población con enfermedades crónicas de salud mental (trastornos depresivos o ansiedad) (tasa de respuesta: 99,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3605; 13803</t>
+          <t>2905; 12982</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8520; 23727</t>
+          <t>8490; 23411</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8039; 24679</t>
+          <t>8078; 24872</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1969; 12213</t>
+          <t>1842; 10976</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>18151; 38182</t>
+          <t>16989; 38474</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25380; 48982</t>
+          <t>25101; 47980</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30809; 55259</t>
+          <t>30576; 56241</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9895; 20295</t>
+          <t>10182; 20384</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>23189; 46694</t>
+          <t>24550; 47234</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>38600; 65547</t>
+          <t>37889; 65386</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>42344; 72665</t>
+          <t>42379; 72951</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14109; 28115</t>
+          <t>14545; 27750</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6843; 20363</t>
+          <t>6042; 20596</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10590; 31647</t>
+          <t>10853; 33408</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8783; 25019</t>
+          <t>8516; 24233</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18834; 40907</t>
+          <t>18800; 42272</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>34186; 59764</t>
+          <t>32984; 59584</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>50273; 81783</t>
+          <t>50001; 82553</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>37601; 65875</t>
+          <t>37253; 65514</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>57226; 83023</t>
+          <t>58139; 84663</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>44434; 73787</t>
+          <t>45587; 74064</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>66666; 103694</t>
+          <t>66445; 104817</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>52317; 85750</t>
+          <t>51969; 83621</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>81247; 118767</t>
+          <t>81392; 117721</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>942; 10462</t>
+          <t>946; 11540</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9694; 27200</t>
+          <t>10035; 27907</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>996; 9763</t>
+          <t>999; 9814</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18907; 38568</t>
+          <t>19444; 38604</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14376; 33443</t>
+          <t>14309; 32751</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27951; 51256</t>
+          <t>27581; 52107</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18742; 39069</t>
+          <t>18099; 38299</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>42544; 64237</t>
+          <t>43398; 64856</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>16986; 37848</t>
+          <t>17213; 37947</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>42082; 71269</t>
+          <t>41665; 69788</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21014; 43617</t>
+          <t>21766; 43010</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>67715; 96861</t>
+          <t>66811; 95463</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2735; 15073</t>
+          <t>3336; 15620</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4234; 20326</t>
+          <t>4140; 17228</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4945; 18530</t>
+          <t>5173; 19384</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15983; 38203</t>
+          <t>15947; 37004</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10019; 26499</t>
+          <t>10305; 26445</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>40651; 66570</t>
+          <t>41560; 68534</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17891; 38800</t>
+          <t>16931; 36223</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>22244; 52500</t>
+          <t>22172; 52504</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16096; 36098</t>
+          <t>15720; 35181</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>48999; 79166</t>
+          <t>46929; 79202</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>25870; 50915</t>
+          <t>27175; 50209</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>44121; 81683</t>
+          <t>45230; 80586</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3371; 14128</t>
+          <t>3409; 12489</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5183; 18370</t>
+          <t>5116; 18990</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5934; 20153</t>
+          <t>6331; 19541</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1198; 7328</t>
+          <t>1188; 7157</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>13257; 31455</t>
+          <t>14407; 32237</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>34547; 58982</t>
+          <t>33536; 57497</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18872; 38607</t>
+          <t>18654; 39116</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>8587; 23701</t>
+          <t>7709; 23254</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>18592; 39082</t>
+          <t>19139; 40265</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>41927; 70073</t>
+          <t>41275; 70252</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>29691; 52418</t>
+          <t>28801; 51663</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>11906; 26956</t>
+          <t>12670; 26614</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 6532</t>
+          <t>0; 6233</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8046; 24974</t>
+          <t>7959; 24099</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2883; 13769</t>
+          <t>2823; 12928</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>19712; 37018</t>
+          <t>19942; 36304</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8450; 25068</t>
+          <t>9128; 23792</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26540; 49330</t>
+          <t>27395; 49691</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24595; 46542</t>
+          <t>25164; 46731</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>31254; 48790</t>
+          <t>30597; 47285</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>10257; 27593</t>
+          <t>10388; 27375</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>38294; 67632</t>
+          <t>37615; 66153</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>30487; 53700</t>
+          <t>30557; 55783</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>55195; 80381</t>
+          <t>54936; 79247</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>11420; 27615</t>
+          <t>11409; 27065</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>23940; 47666</t>
+          <t>23622; 49699</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8459; 26181</t>
+          <t>8352; 25026</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>33106; 61519</t>
+          <t>32806; 60436</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>39724; 68592</t>
+          <t>38333; 66033</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>48652; 78810</t>
+          <t>48795; 78056</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>44547; 74685</t>
+          <t>46191; 76981</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>49286; 135942</t>
+          <t>48289; 137379</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>54734; 87443</t>
+          <t>54500; 86196</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>80430; 117838</t>
+          <t>78896; 120523</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>56919; 91352</t>
+          <t>57987; 93739</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>90330; 176943</t>
+          <t>92420; 177779</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>31747; 56377</t>
+          <t>32070; 59047</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>14869; 35745</t>
+          <t>14089; 34524</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>23595; 46658</t>
+          <t>22994; 44982</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>13834; 51523</t>
+          <t>14877; 54877</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>44323; 75351</t>
+          <t>44506; 73742</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>55951; 87286</t>
+          <t>53557; 87362</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>76710; 114751</t>
+          <t>76309; 115450</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>70008; 97665</t>
+          <t>70302; 98047</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>82102; 121521</t>
+          <t>82536; 124677</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>74861; 114061</t>
+          <t>76149; 116575</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>106291; 151517</t>
+          <t>106512; 154082</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>76151; 147523</t>
+          <t>72753; 148206</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>82495; 121211</t>
+          <t>82672; 122507</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>119409; 169596</t>
+          <t>118968; 168850</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>92138; 133487</t>
+          <t>91379; 132771</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>156248; 231927</t>
+          <t>155788; 229127</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>226831; 288464</t>
+          <t>226997; 288276</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>364180; 441185</t>
+          <t>366728; 444837</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>327383; 399455</t>
+          <t>323651; 398752</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>333079; 458157</t>
+          <t>334413; 455450</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>324573; 398476</t>
+          <t>326547; 396959</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>504880; 599533</t>
+          <t>506773; 597587</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>425952; 515234</t>
+          <t>434571; 519549</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>533889; 673135</t>
+          <t>525435; 669137</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P1423-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P1423-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,06; 4,76</t>
+          <t>1,29; 4,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,88; 7,94</t>
+          <t>2,92; 7,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,75; 8,47</t>
+          <t>2,75; 8,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,52</t>
+          <t>0,53; 3,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,51; 14,75</t>
+          <t>6,85; 14,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,74; 16,7</t>
+          <t>8,64; 16,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,59; 19,48</t>
+          <t>10,67; 19,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,52; 7,04</t>
+          <t>3,51; 7,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,6; 8,85</t>
+          <t>4,66; 9,19</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,51; 11,23</t>
+          <t>6,53; 11,33</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,28; 12,52</t>
+          <t>7,39; 12,78</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,42; 4,62</t>
+          <t>2,38; 4,53</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,81%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,23; 4,18</t>
+          <t>1,27; 4,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,15; 6,61</t>
+          <t>1,96; 6,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,69; 4,82</t>
+          <t>1,71; 4,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,63; 8,15</t>
+          <t>3,87; 8,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,55; 11,82</t>
+          <t>6,79; 11,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,55; 15,76</t>
+          <t>9,77; 15,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,12; 12,52</t>
+          <t>7,32; 12,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,29; 16,44</t>
+          <t>11,33; 16,23</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,57; 7,43</t>
+          <t>4,4; 7,29</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,46; 10,18</t>
+          <t>6,42; 10,21</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,07; 8,15</t>
+          <t>5,1; 8,33</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,88; 11,39</t>
+          <t>8,23; 11,66</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,36%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,62</t>
+          <t>0,29; 3,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,1; 8,61</t>
+          <t>3,34; 8,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,08</t>
+          <t>0,32; 3,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,15; 12,21</t>
+          <t>6,4; 12,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,27; 9,76</t>
+          <t>4,42; 9,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,09; 15,28</t>
+          <t>8,1; 15,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,38; 11,39</t>
+          <t>5,22; 11,22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,43; 18,58</t>
+          <t>12,41; 18,34</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,63; 5,8</t>
+          <t>2,61; 5,7</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,26; 10,49</t>
+          <t>6,43; 10,8</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,32; 6,57</t>
+          <t>3,15; 6,63</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,04; 14,35</t>
+          <t>10,31; 14,49</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,56%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 4,35</t>
+          <t>0,93; 4,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,11; 4,61</t>
+          <t>1,13; 4,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,4; 5,24</t>
+          <t>1,55; 5,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,1; 11,84</t>
+          <t>4,69; 10,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,77; 7,12</t>
+          <t>2,76; 6,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,69; 17,62</t>
+          <t>10,21; 17,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,37; 9,35</t>
+          <t>4,33; 9,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,66; 11,04</t>
+          <t>7,71; 12,91</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,82</t>
+          <t>2,13; 4,75</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,15; 10,38</t>
+          <t>6,34; 10,33</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,59; 6,63</t>
+          <t>3,48; 6,57</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,74; 10,22</t>
+          <t>6,82; 10,56</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,68; 6,14</t>
+          <t>1,65; 6,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,41; 8,93</t>
+          <t>2,59; 8,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,0; 9,25</t>
+          <t>2,74; 8,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,66; 4,0</t>
+          <t>0,58; 3,55</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,94; 15,52</t>
+          <t>6,78; 15,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,27; 26,18</t>
+          <t>15,54; 26,57</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,53; 17,89</t>
+          <t>8,75; 17,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,98; 8,99</t>
+          <t>5,37; 10,44</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,66; 9,8</t>
+          <t>4,78; 10,0</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,55; 16,25</t>
+          <t>9,68; 15,88</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,7; 12,02</t>
+          <t>6,62; 12,0</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,9; 6,08</t>
+          <t>3,4; 6,53</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,48%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,3</t>
+          <t>0,0; 2,24</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,91; 8,8</t>
+          <t>2,84; 8,5</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,07; 4,91</t>
+          <t>1,12; 5,09</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,4; 13,46</t>
+          <t>7,33; 13,36</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,28; 8,55</t>
+          <t>3,28; 8,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,85; 17,87</t>
+          <t>9,18; 17,67</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,21; 17,11</t>
+          <t>8,68; 17,15</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11,9; 18,39</t>
+          <t>11,85; 18,45</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,99</t>
+          <t>2,0; 4,9</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6,81; 11,98</t>
+          <t>7,11; 12,15</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5,7; 10,4</t>
+          <t>5,47; 10,33</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,43; 15,05</t>
+          <t>10,47; 14,71</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>11,31%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,4</t>
+          <t>1,82; 4,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,56; 7,5</t>
+          <t>3,63; 7,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,27; 3,81</t>
+          <t>1,32; 3,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,26; 9,68</t>
+          <t>5,37; 9,64</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,01; 10,35</t>
+          <t>5,94; 10,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,03; 11,25</t>
+          <t>7,15; 11,52</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,68; 11,14</t>
+          <t>6,49; 10,97</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,69; 16,18</t>
+          <t>12,8; 17,7</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,35; 6,88</t>
+          <t>4,42; 7,03</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5,82; 8,88</t>
+          <t>5,94; 8,61</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4,3; 6,95</t>
+          <t>4,33; 7,09</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,27; 12,06</t>
+          <t>9,68; 12,88</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,31; 7,94</t>
+          <t>4,44; 7,94</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,81; 4,43</t>
+          <t>1,95; 4,49</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,95; 5,78</t>
+          <t>2,83; 5,58</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,6; 5,91</t>
+          <t>3,73; 7,07</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,68; 9,41</t>
+          <t>5,72; 9,85</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,51; 10,62</t>
+          <t>6,6; 10,52</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,24; 13,97</t>
+          <t>9,22; 14,06</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>9,8; 13,66</t>
+          <t>9,92; 13,9</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5,4; 8,16</t>
+          <t>5,4; 7,9</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4,75; 7,28</t>
+          <t>4,69; 7,21</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6,64; 9,6</t>
+          <t>6,52; 9,55</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,42; 9,0</t>
+          <t>7,35; 9,72</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>9,24%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,52; 3,74</t>
+          <t>2,54; 3,71</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,47; 4,93</t>
+          <t>3,43; 4,98</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,69; 3,91</t>
+          <t>2,71; 3,9</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,5; 6,62</t>
+          <t>5,29; 7,01</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,72; 8,53</t>
+          <t>6,57; 8,42</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,32; 12,51</t>
+          <t>10,44; 12,49</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,13; 11,25</t>
+          <t>9,12; 11,26</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>9,01; 12,27</t>
+          <t>11,32; 13,2</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,91; 5,96</t>
+          <t>4,78; 5,92</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7,26; 8,56</t>
+          <t>7,23; 8,51</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6,26; 7,49</t>
+          <t>6,26; 7,51</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>7,33; 9,33</t>
+          <t>8,54; 9,81</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5477</t>
+          <t>5075</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14657</t>
+          <t>15936</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20134</t>
+          <t>21011</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2905; 12982</t>
+          <t>3532; 13511</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8490; 23411</t>
+          <t>8604; 23194</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8078; 24872</t>
+          <t>8086; 24256</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1842; 10976</t>
+          <t>1682; 10341</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>16989; 38474</t>
+          <t>17863; 37409</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25101; 47980</t>
+          <t>24831; 47621</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30576; 56241</t>
+          <t>30791; 55414</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10182; 20384</t>
+          <t>11093; 22520</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>24550; 47234</t>
+          <t>24882; 49038</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>37889; 65386</t>
+          <t>37975; 65934</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>42379; 72951</t>
+          <t>43023; 74463</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14545; 27750</t>
+          <t>15082; 28783</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>28758</t>
+          <t>30495</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>69824</t>
+          <t>75192</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98582</t>
+          <t>105687</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6042; 20596</t>
+          <t>6284; 20306</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10853; 33408</t>
+          <t>9925; 31015</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8516; 24233</t>
+          <t>8608; 24092</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18800; 42272</t>
+          <t>20540; 44131</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>32984; 59584</t>
+          <t>34201; 59789</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>50001; 82553</t>
+          <t>51151; 82987</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>37253; 65514</t>
+          <t>38279; 67441</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>58139; 84663</t>
+          <t>61937; 88719</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>45587; 74064</t>
+          <t>43900; 72729</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>66445; 104817</t>
+          <t>66044; 105140</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>51969; 83621</t>
+          <t>52341; 85463</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>81392; 117721</t>
+          <t>88692; 125601</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27403</t>
+          <t>29020</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>52976</t>
+          <t>54094</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>80378</t>
+          <t>83115</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>946; 11540</t>
+          <t>928; 11116</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10035; 27907</t>
+          <t>10809; 27498</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>999; 9814</t>
+          <t>1008; 10498</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19444; 38604</t>
+          <t>20234; 39326</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14309; 32751</t>
+          <t>14811; 32638</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27581; 52107</t>
+          <t>27631; 51976</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18099; 38299</t>
+          <t>17568; 37721</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>43398; 64856</t>
+          <t>44234; 65366</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17213; 37947</t>
+          <t>17071; 37325</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>41665; 69788</t>
+          <t>42781; 71809</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21766; 43010</t>
+          <t>20598; 43443</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>66811; 95463</t>
+          <t>69337; 97456</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24838</t>
+          <t>26633</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>38582</t>
+          <t>41431</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>63420</t>
+          <t>68063</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3336; 15620</t>
+          <t>3327; 16022</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4140; 17228</t>
+          <t>4231; 18114</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5173; 19384</t>
+          <t>5753; 19646</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15947; 37004</t>
+          <t>17495; 40098</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10305; 26445</t>
+          <t>10263; 25583</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>41560; 68534</t>
+          <t>39714; 66641</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16931; 36223</t>
+          <t>16765; 37758</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>22172; 52504</t>
+          <t>32541; 54491</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>15720; 35181</t>
+          <t>15544; 34671</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>46929; 79202</t>
+          <t>48369; 78803</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>27175; 50209</t>
+          <t>26371; 49737</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>45230; 80586</t>
+          <t>54236; 83927</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2986</t>
+          <t>3137</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>16101</t>
+          <t>17019</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>19087</t>
+          <t>20156</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3409; 12489</t>
+          <t>3355; 12721</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5116; 18990</t>
+          <t>5509; 18601</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6331; 19541</t>
+          <t>5781; 18605</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1188; 7157</t>
+          <t>1184; 7294</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>14407; 32237</t>
+          <t>14080; 31167</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>33536; 57497</t>
+          <t>34116; 58353</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18654; 39116</t>
+          <t>19124; 38324</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7709; 23254</t>
+          <t>12286; 23903</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>19139; 40265</t>
+          <t>19642; 41095</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>41275; 70252</t>
+          <t>41820; 68642</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>28801; 51663</t>
+          <t>28466; 51579</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>12670; 26614</t>
+          <t>14774; 28362</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>27441</t>
+          <t>27413</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>38794</t>
+          <t>39311</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>66235</t>
+          <t>66724</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 6233</t>
+          <t>0; 6065</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7959; 24099</t>
+          <t>7781; 23297</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2823; 12928</t>
+          <t>2944; 13390</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>19942; 36304</t>
+          <t>19854; 36178</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9128; 23792</t>
+          <t>9131; 24539</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>27395; 49691</t>
+          <t>25526; 49140</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25164; 46731</t>
+          <t>23718; 46837</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>30597; 47285</t>
+          <t>31267; 48651</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>10388; 27375</t>
+          <t>10990; 26905</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>37615; 66153</t>
+          <t>39276; 67073</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>30557; 55783</t>
+          <t>29342; 55397</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>54936; 79247</t>
+          <t>55961; 78629</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>45270</t>
+          <t>52462</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>98369</t>
+          <t>116236</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>143639</t>
+          <t>168698</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>11409; 27065</t>
+          <t>11209; 27305</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>23622; 49699</t>
+          <t>24055; 48831</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8352; 25026</t>
+          <t>8645; 23991</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>32806; 60436</t>
+          <t>38654; 69367</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>38333; 66033</t>
+          <t>37912; 66929</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>48795; 78056</t>
+          <t>49621; 79965</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>46191; 76981</t>
+          <t>44890; 75862</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>48289; 137379</t>
+          <t>98795; 136658</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>54500; 86196</t>
+          <t>55422; 88063</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>78896; 120523</t>
+          <t>80633; 116834</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>57987; 93739</t>
+          <t>58427; 95602</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>92420; 177779</t>
+          <t>144418; 192182</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>35195</t>
+          <t>40812</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>83824</t>
+          <t>97412</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>119019</t>
+          <t>138224</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>32070; 59047</t>
+          <t>33022; 59087</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>14089; 34524</t>
+          <t>15165; 34980</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>22994; 44982</t>
+          <t>21997; 43481</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>14877; 54877</t>
+          <t>29731; 56450</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>44506; 73742</t>
+          <t>44841; 77174</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>53557; 87362</t>
+          <t>54272; 86499</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>76309; 115450</t>
+          <t>76173; 116120</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>70302; 98047</t>
+          <t>82450; 115514</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>82536; 124677</t>
+          <t>82417; 120581</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>76149; 116575</t>
+          <t>75149; 115454</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>106512; 154082</t>
+          <t>104679; 153208</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>72753; 148206</t>
+          <t>119798; 158383</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>197367</t>
+          <t>215047</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>413127</t>
+          <t>456631</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>610494</t>
+          <t>671678</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>82672; 122507</t>
+          <t>83266; 121468</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>118968; 168850</t>
+          <t>117403; 170544</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>91379; 132771</t>
+          <t>91904; 132452</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>155788; 229127</t>
+          <t>186900; 247797</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>226997; 288276</t>
+          <t>222029; 284522</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>366728; 444837</t>
+          <t>371315; 444017</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>323651; 398752</t>
+          <t>323335; 399186</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>334413; 455450</t>
+          <t>422986; 493459</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>326547; 396959</t>
+          <t>318267; 393864</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>506773; 597587</t>
+          <t>504603; 594476</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>434571; 519549</t>
+          <t>434479; 521099</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>525435; 669137</t>
+          <t>620917; 712908</t>
         </is>
       </c>
     </row>
